--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-10-31</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
     <t>健康保険における被保険者証番号の枝番を示す拡張</t>
   </si>
   <si>
-    <t>健康保険における被保険者証番号を示す拡張。2桁の全角数字文字列。一桁の場合には先頭に０をつけて2桁にする。</t>
+    <t>健康保険における被保険者証番号を示す拡張。2桁の半角数字文字列。一桁の場合には先頭に0をつけて2桁にする。</t>
   </si>
   <si>
     <t>Coverage.modifierExtension</t>
@@ -552,37 +552,328 @@
     <t>Business Identifier for the coverage　このカバレッジに割り当てられた一意の識別子【詳細参照】</t>
   </si>
   <si>
-    <t>A unique identifier assigned to this coverage.  
-このカバレッジに割り当てられた一意の識別子。</t>
+    <t>A unique identifier assigned to this coverage.  このカバレッジに割り当てられた一意の識別子。</t>
+  </si>
+  <si>
+    <t>Allows coverages to be distinguished and referenced.  
+カバレッジを区別して参照できるようにする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>IN1-2</t>
+  </si>
+  <si>
+    <t>C.32, C.33, C.39</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者識別子　例）00012345:あいう:１８７:05</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
+  </si>
+  <si>
+    <t>「被保険者識別子」の文字列仕様を参照のこと</t>
+  </si>
+  <si>
+    <t>カバレッジを区別し、参照することができます。 / Allows coverages to be distinguished and referenced.</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.use</t>
+  </si>
+  <si>
+    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>この識別子の目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>識別子の説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.system</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberID</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.value</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.value</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
+本仕様では、以下、これを「被保険者識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
+被保険者識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
+要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者識別子」の文字列仕様を参照のこと</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
+  </si>
+  <si>
+    <t>保険者情報を設定</t>
+  </si>
+  <si>
+    <t>保険者情報として[JP_Organization](StructureDefinition-jp-organization.html)を設定する。</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者識別子（CSV形式）　"00012345","１２－３４","５６７８","00"</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報を囲み文字をダブルクォーテーション、区切りをカンマにて連結する</t>
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
 カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
-ルール："{被保険者記号}","{被保険者番号}","{枝番}"  
-例："１２－３４","５６７８","００"</t>
-  </si>
-  <si>
-    <t>Allows coverages to be distinguished and referenced.  
-カバレッジを区別して参照できるようにする。</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>C02</t>
-  </si>
-  <si>
-    <t>IN1-2</t>
-  </si>
-  <si>
-    <t>C.32, C.33, C.39</t>
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberCsvID</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.value</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。</t>
+  </si>
+  <si>
+    <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
+カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+【JP Core仕様】保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"
+要素を省略する、とある場合には、長さ０の文字列とする。</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>保険者情報</t>
+  </si>
+  <si>
+    <t>健康保険等の保険者情報を設定する。[JP_Organization](StructureDefinition-jp-organization.html)をリソースにて表現する</t>
   </si>
   <si>
     <t>Coverage.status</t>
@@ -603,9 +894,6 @@
 「ドラフト」リソースはさらに編集される可能性があり、「アクティブ」リソースは不変であり、ステータスが「キャンセル」に変更されるだけである可能性があるため、リソースのステータスを追跡する必要がある。</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>リソースインスタンスの状態を指定するコード。 / A code specifying the state of the resource instance.</t>
   </si>
   <si>
@@ -622,10 +910,6 @@
   </si>
   <si>
     <t>Coverage.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Coverage category such as medical or accident　医療保険や事故補償のような分類</t>
@@ -713,10 +997,6 @@
   </si>
   <si>
     <t>Coverage.subscriberId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>ID assigned to the subscriber　被保険者に割り当てられたID</t>
@@ -730,8 +1010,8 @@
 保険者は、連絡や請求（デジタルおよびその他）でこの識別子を要求する。  
 保険会社は、通信および請求（デジタルおよびその他）でこの識別子を要求する。  
 【JP Core仕様】被保険者記号と番号を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
-ルール："{被保険者記号}","{被保険者番号}"  
-例："１２－３４","５６７８"</t>
+ルール：{被保険者記号}:{被保険者番号}  
+例："あいう","５６７８"</t>
   </si>
   <si>
     <t>Coverage.beneficiary</t>
@@ -778,7 +1058,7 @@
 一部の補償では、単一の識別子が加入者に発行され、次に一意の従属番号が各受益者に発行される。  
 一部の保険では、単一の識別子が加入者に発行され、その後、各受益者に固有の扶養番号が発行される。  
 【JP Core仕様】医療保険で本リソースを使用する場合には、この要素に拡張 InsuredPersonSubNumberに設定した値と同じ、被保険者番号の枝番号全角2桁を設定する。  
-例："００"</t>
+例："00"</t>
   </si>
   <si>
     <t>C17</t>
@@ -808,9 +1088,6 @@
 　2 被扶養者</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
@@ -821,10 +1098,6 @@
   </si>
   <si>
     <t>Coverage.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>カバレッジの開始日と終了日 / Coverage start and end dates</t>
@@ -867,7 +1140,7 @@
 </t>
   </si>
   <si>
-    <t>ポリシーの発行者 / Issuer of the policy</t>
+    <t>支払者に関する情報</t>
   </si>
   <si>
     <t>The program or plan underwriter or payor including both insurance and non-insurance agreements, such as patient-pay agreements.  
@@ -921,28 +1194,7 @@
     <t>Coverage.class.id</t>
   </si>
   <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Coverage.class.extension</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Coverage.class.modifierExtension</t>
@@ -1128,9 +1380,6 @@
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.coding</t>
@@ -1734,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP58"/>
+  <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.57421875" customWidth="true" bestFit="true"/>
@@ -1773,7 +2022,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.53125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="59.44921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="51.2734375" customWidth="true" bestFit="true"/>
@@ -3387,10 +3636,10 @@
         <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3427,16 +3676,14 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>168</v>
@@ -3477,15 +3724,17 @@
         <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
@@ -3494,25 +3743,25 @@
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3537,13 +3786,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3561,13 +3810,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3576,30 +3825,30 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3619,23 +3868,19 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3659,13 +3904,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3695,22 +3940,22 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3718,21 +3963,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3741,23 +3986,21 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3793,57 +4036,57 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3860,25 +4103,25 @@
         <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3903,13 +4146,13 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3927,7 +4170,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3945,27 +4188,27 @@
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3988,17 +4231,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4023,13 +4268,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -4047,7 +4292,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4065,19 +4310,19 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -4085,7 +4330,7 @@
         <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4108,7 +4353,7 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>224</v>
@@ -4127,7 +4372,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>80</v>
@@ -4169,10 +4414,10 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>90</v>
@@ -4184,30 +4429,30 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4215,7 +4460,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>90</v>
@@ -4230,20 +4475,18 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4291,7 +4534,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4309,16 +4552,16 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4326,10 +4569,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4349,23 +4592,19 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4389,13 +4628,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4413,7 +4652,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4431,16 +4670,16 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4448,10 +4687,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4474,20 +4713,18 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4535,7 +4772,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4550,13 +4787,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4573,18 +4810,20 @@
         <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4596,7 +4835,7 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>256</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>257</v>
@@ -4608,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>260</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4657,10 +4896,10 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>82</v>
@@ -4672,30 +4911,30 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>263</v>
+        <v>178</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4706,7 +4945,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -4718,20 +4957,16 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4779,25 +5014,25 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4814,21 +5049,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4840,15 +5075,17 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>195</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4885,37 +5122,37 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -4932,44 +5169,46 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>202</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -4993,13 +5232,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5017,25 +5256,25 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -5044,7 +5283,7 @@
         <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5052,45 +5291,45 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5115,13 +5354,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -5139,25 +5378,25 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
@@ -5166,7 +5405,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5174,10 +5413,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5200,26 +5439,26 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>286</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>289</v>
+        <v>227</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>80</v>
@@ -5237,13 +5476,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -5261,10 +5500,10 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -5279,7 +5518,7 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
@@ -5288,7 +5527,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5296,10 +5535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5322,20 +5561,18 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5383,10 +5620,10 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>90</v>
@@ -5401,27 +5638,27 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5444,18 +5681,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>242</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>243</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5503,7 +5738,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5521,27 +5756,27 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>248</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5564,20 +5799,18 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5625,7 +5858,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5643,7 +5876,7 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>253</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
@@ -5652,7 +5885,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5660,10 +5893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5671,7 +5904,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -5680,23 +5913,25 @@
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>218</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5721,13 +5956,13 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5745,10 +5980,10 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5760,16 +5995,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -5780,21 +6015,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5803,22 +6038,22 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5843,13 +6078,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -5867,13 +6102,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -5888,13 +6123,13 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5902,10 +6137,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5925,19 +6160,23 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>218</v>
+        <v>293</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5985,7 +6224,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5997,44 +6236,44 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6043,21 +6282,23 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6105,80 +6346,78 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6227,45 +6466,45 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6273,7 +6512,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -6288,19 +6527,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6325,13 +6564,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6349,10 +6588,10 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>90</v>
@@ -6364,30 +6603,30 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6407,19 +6646,23 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6467,7 +6710,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6479,22 +6722,22 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6502,21 +6745,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6528,18 +6771,20 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6563,55 +6808,55 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6636,7 +6881,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6648,19 +6893,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6709,13 +6954,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -6724,13 +6969,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6755,10 +7000,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6767,19 +7012,23 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>218</v>
+        <v>344</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6827,49 +7076,49 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6888,18 +7137,20 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>354</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>278</v>
+        <v>356</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6935,19 +7186,19 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>279</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6959,13 +7210,13 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6982,10 +7233,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7005,23 +7256,19 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>189</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7069,7 +7316,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>191</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7081,13 +7328,13 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>192</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7096,7 +7343,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7104,21 +7351,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7127,19 +7374,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>195</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>355</v>
+        <v>196</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>356</v>
+        <v>165</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7189,25 +7436,25 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>198</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>358</v>
+        <v>192</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7216,7 +7463,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7224,45 +7471,45 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>363</v>
+        <v>165</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>364</v>
+        <v>166</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7317,19 +7564,19 @@
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>366</v>
+        <v>133</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7338,7 +7585,7 @@
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7346,10 +7593,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7357,7 +7604,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7372,17 +7619,19 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7407,13 +7656,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7431,10 +7680,10 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>90</v>
@@ -7449,7 +7698,7 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7458,7 +7707,7 @@
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7466,10 +7715,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7477,7 +7726,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7492,19 +7741,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7553,10 +7802,10 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7571,27 +7820,27 @@
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7614,19 +7863,17 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7675,7 +7922,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7693,27 +7940,27 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7721,7 +7968,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -7736,19 +7983,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7797,10 +8044,10 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>90</v>
@@ -7821,21 +8068,21 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7846,7 +8093,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7855,20 +8102,20 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>320</v>
+        <v>394</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7917,13 +8164,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -7941,7 +8188,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -7952,21 +8199,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7978,16 +8225,20 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>272</v>
+        <v>398</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8035,25 +8286,25 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>274</v>
+        <v>396</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -8077,14 +8328,14 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8096,17 +8347,15 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8155,25 +8404,25 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8197,7 +8446,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>281</v>
+        <v>162</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8210,26 +8459,24 @@
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>283</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8277,7 +8524,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8295,7 +8542,7 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8319,36 +8566,38 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>363</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>407</v>
+        <v>166</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8373,13 +8622,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8397,25 +8646,25 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>365</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8432,10 +8681,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8458,17 +8707,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8493,13 +8744,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8517,7 +8768,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8552,10 +8803,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8578,20 +8829,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>376</v>
+        <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>416</v>
+        <v>189</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8639,7 +8886,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>415</v>
+        <v>191</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8651,13 +8898,13 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -8674,14 +8921,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8700,20 +8947,18 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>421</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>422</v>
+        <v>195</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>423</v>
+        <v>196</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8749,19 +8994,19 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>198</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8773,25 +9018,2199 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AO58" t="s" s="2">
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AP58" t="s" s="2">
-        <v>210</v>
+      <c r="M62" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -587,13 +587,13 @@
     <t>insuranceIdentifier</t>
   </si>
   <si>
-    <t>被保険者識別子　例）00012345:あいう:１８７:05</t>
-  </si>
-  <si>
-    <t>被保険者識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
-  </si>
-  <si>
-    <t>「被保険者識別子」の文字列仕様を参照のこと</t>
+    <t>被保険者個人識別子　例）00012345:あいう:１８７:05</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
+  </si>
+  <si>
+    <t>「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
     <t>カバレッジを区別し、参照することができます。 / Allows coverages to be distinguished and referenced.</t>
@@ -727,7 +727,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberID</t>
+    <t>http://jpfhir.jp/fhir/clins/Idsystem/JP_Insurance_memberID</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -745,10 +745,10 @@
     <t>Coverage.identifier.value</t>
   </si>
   <si>
-    <t>被保険者識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
-本仕様では、以下、これを「被保険者識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
-被保険者識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
-要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者識別子」の文字列仕様を参照のこと</t>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
+本仕様では、以下、これを「被保険者個人識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
+被保険者個人識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
+要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
     <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
@@ -847,7 +847,7 @@
     <t>Coverage.identifier:insuranceCsvIdentifier.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberCsvID</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/JP_Coverage_id</t>
   </si>
   <si>
     <t>Coverage.identifier:insuranceCsvIdentifier.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -921,7 +921,7 @@
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
 すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。  
-【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”urn:oid:1.2.392.100495.20.2.61”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
+【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
   </si>
   <si>
     <t>The order of application of coverages is dependent on the types of coverage.  
@@ -1083,7 +1083,7 @@
   <si>
     <t>To determine relationship between the patient and the subscriber to determine coordination of benefits.  
 患者と加入者の関係を決定し、給付の調整を決定する。  
-【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される被保険者区分コード（system=”urn:oid:1.2.392.100495.20.2.62”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１２が使用できる。  
+【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される被保険者区分コード（system=”http://jpfhir.jp/fhir/core/mhlw/CodeSystem/InsuredPersonCategory”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１２が使用できる。  
 　1 被保険者  
 　2 被扶養者</t>
   </si>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -280,7 +280,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -318,16 +318,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -453,7 +453,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -645,22 +645,22 @@
     <t>Coverage.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -682,22 +682,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -715,16 +715,16 @@
     <t>Coverage.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/clins/Idsystem/JP_Insurance_memberID</t>
@@ -751,7 +751,7 @@
 要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -776,7 +776,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -280,7 +280,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -879,7 +879,7 @@
     <t>Coverage.status</t>
   </si>
   <si>
-    <t>アクティブ|キャンセル|ドラフト|エラーに入った / active | cancelled | draft | entered-in-error</t>
+    <t>アクティブ|キャンセル|ドラフト|エラー入力 / active | cancelled | draft | entered-in-error</t>
   </si>
   <si>
     <t>The status of the resource instance.  

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -1986,17 +1986,17 @@
   <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="21.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="128.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="110.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2005,28 +2005,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="207.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.84375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.3046875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.69140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="59.44921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="51.2734375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="62.85546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="50.96484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="43.95703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="53.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -372,7 +372,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -700,7 +700,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -931,7 +931,7 @@
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-type|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -1091,7 +1091,7 @@
     <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship|4.0.1</t>
   </si>
   <si>
     <t>C03</t>
@@ -1236,7 +1236,7 @@
     <t>ポリシー分類、例。グループ、プラン、クラスなど / The policy classifications, eg. Group, Plan, Class, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-class</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-class|4.0.1</t>
   </si>
   <si>
     <t>Coverage.class.value</t>
@@ -1373,7 +1373,7 @@
     <t>患者の自己負担が指定されているサービスの種類。 / The types of services to which patient copayments are specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.id</t>
@@ -1564,7 +1564,7 @@
     <t>Coverage.costToBeneficiary.value[x]</t>
   </si>
   <si>
-    <t>Quantity {SimpleQuantity}
+    <t>Quantity {SimpleQuantity|4.0.1}
 Money</t>
   </si>
   <si>
@@ -1622,7 +1622,7 @@
     <t>部品からの例外の種類またはCopaysなどの財務義務の完全な価値。 / The types of exceptions from the part or full value of financial obligations such as copays.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.exception.period</t>
@@ -1660,7 +1660,7 @@
     <t>Coverage.contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Contract)
+    <t xml:space="preserve">Reference(Contract|4.0.1)
 </t>
   </si>
   <si>
@@ -2011,7 +2011,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.83203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -1226,7 +1226,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および前後の調整を管理するための独自の構造を提供することが望ましい。</t>
+すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>The insurer issued label for a specific health card value.  

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>The Coverage resource contains the insurance card level information, which is customary to provide on claims and other communications between providers and insurers.  
-Coverageには、保険証レベルの情報が含まれている。これは、保険金請求やプロバイダと保険会社間のその他の通信で提供するのが通例である。</t>
+Coverageには、保険証レベルの情報が含まれている。これは、保険金請求や医療提供者と保険会社間のその他の通信で提供するのが通例である。</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -549,14 +549,14 @@
 </t>
   </si>
   <si>
-    <t>Business Identifier for the coverage　このカバレッジに割り当てられた一意の識別子【詳細参照】</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this coverage.  このカバレッジに割り当てられた一意の識別子。</t>
+    <t>Business Identifier for the coverage　この保険適用情報に割り当てられた一意の識別子【詳細参照】</t>
+  </si>
+  <si>
+    <t>A unique identifier assigned to this coverage.  この保険適用情報に割り当てられた一意の識別子。</t>
   </si>
   <si>
     <t>Allows coverages to be distinguished and referenced.  
-カバレッジを区別して参照できるようにする。</t>
+保険適用情報を区別して参照できるようにする。</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -826,7 +826,7 @@
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
-カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+保険適用情報のメイン（および場合によっては唯一の）識別子-多くの場合、会員番号、証明書番号、個人健康識別子、または症例IDと呼ばれる。  
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
 ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
 例："00012345","１２－３４","５６７８","00"</t>
@@ -857,7 +857,7 @@
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
-カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+保険適用情報のメイン（および場合によっては唯一の）識別子-多くの場合、会員番号、証明書番号、個人健康識別子、または症例IDと呼ばれる。  
 【JP Core仕様】保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
 ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
 例："00012345","１２－３４","５６７８","00"
@@ -887,7 +887,7 @@
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains the code entered-in-error that marks the coverage as not currently valid.  
-ステータスには、カバレッジが現在無効であることを示すエラー入力されたコードが含まれているため、この要素は修飾子としてラベル付けされる。</t>
+ステータスには、保険適用情報が現在無効であることを示すエラー入力されたコードが含まれているため、この要素は修飾子としてラベル付けされる。</t>
   </si>
   <si>
     <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.  
@@ -925,7 +925,7 @@
   </si>
   <si>
     <t>The order of application of coverages is dependent on the types of coverage.  
-カバレッジの適用順序は、カバレッジのタイプによって異なる。</t>
+保険適用の適用順序は、保険適用のタイプによって異なる。</t>
   </si>
   <si>
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
@@ -1226,7 +1226,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
+すべての用語の使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>The insurer issued label for a specific health card value.  
@@ -1291,7 +1291,7 @@
   </si>
   <si>
     <t>The order of applicability of this coverage relative to other coverages which are currently in force. Note, there may be gaps in the numbering and this does not imply primary, secondary etc. as the specific positioning of coverages depends upon the episode of care.  
-現在適用されている他の保障と比較して、この保障の適用可能性が高い順に記載されている。なお、ナンバリングにギャップがある場合があり、カバーの具体的な位置づけはケアのエピソードに依存するため、一次、二次などを意味するものではない。</t>
+現在適用されている他の保障と比較して、この保障の適用可能性が高い順に記載されている。なお、採番にギャップがある場合があり、適用範囲の具体的な位置づけは診療エピソードに依存するため、一次、二次などを意味するものではない。</t>
   </si>
   <si>
     <t>32 bit number; for values larger than this, use decimal  
@@ -1310,7 +1310,7 @@
   </si>
   <si>
     <t>The insurer-specific identifier for the insurer-defined network of providers to which the beneficiary may seek treatment which will be covered at the 'in-network' rate, otherwise 'out of network' terms and conditions apply.  
-保険者が定義したプロバイダの保険者定義ネットワークの保険者固有の識別子で、被保険者が「ネットワーク内」の料金でカバーされる治療を受けることができるが、そうでなければ「ネットワーク外」の条件が適用される。</t>
+保険者が定義した医療提供者の保険者定義ネットワークの保険者固有の識別子で、被保険者が「ネットワーク内」の料金でカバーされる治療を受けることができるが、そうでなければ「ネットワーク外」の条件が適用される。</t>
   </si>
   <si>
     <t>Used in referral for treatment and in claims processing.  
@@ -1472,8 +1472,7 @@
     <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size  
-自己負担率を表すコード　"copaypct"</t>
+    <t>自己負担率を表すコード　"copaypct"</t>
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -920,7 +920,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。  
+すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。  
 【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
   </si>
   <si>
@@ -1226,7 +1226,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべての用語の使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
+すべての用語の使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用し、テキスト、`Coding`、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>The insurer issued label for a specific health card value.  

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -1300,7 +1300,7 @@
   <si>
     <t>Used in managing the coordination of benefits.  
 保険給付の調整管理に使用する。  
-【JP Core仕様】公費情報で本リソースを使用する場合で、複数の公費負担情報がある場合に、その適用順序番号を示す１，２，３．．．を設定する。</t>
+【JP Core仕様】公費情報で本リソースを使用する場合で、複数の公費負担情報がある場合に、その適用順序番号を示す１、２、３…を設定する。</t>
   </si>
   <si>
     <t>Coverage.network</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-coverage.xlsx
@@ -947,7 +947,7 @@
 </t>
   </si>
   <si>
-    <t>Owner of the policy　ポリシの所有者</t>
+    <t>Owner of the policy　ポリシーの所有者</t>
   </si>
   <si>
     <t>The party who 'owns' the insurance policy.  
@@ -959,7 +959,7 @@
   </si>
   <si>
     <t>This provides employer information in the case of Worker's Compensation and other policies.  
-これは、労働者災害補償およびその他のポリシの場合に雇用者情報を提供する。</t>
+これは、労働者災害補償およびその他のポリシーの場合に雇用者情報を提供する。</t>
   </si>
   <si>
     <t>FiveWs.subject</t>
@@ -985,7 +985,7 @@
   </si>
   <si>
     <t>The party who has signed-up for or 'owns' the contractual relationship to the policy or to whom the benefit of the policy for services rendered to them or their family is due.  
-ポリシにサインアップした、またはポリシとの契約関係を「所有」している当事者、またはポリシの利益が彼らまたはその家族に提供されることになっている当事者。</t>
+ポリシーにサインアップした、またはポリシーとの契約関係を「所有」している当事者、またはポリシーの利益が彼らまたはその家族に提供されることになっている当事者。</t>
   </si>
   <si>
     <t>May be self or a parent in the case of dependents.  
@@ -993,7 +993,7 @@
   </si>
   <si>
     <t>This is the party who is entitled to the benefits under the policy.  
-これは、ポリシに基づいて給付を受ける権利を有する当事者である。</t>
+これは、ポリシーに基づいて給付を受ける権利を有する当事者である。</t>
   </si>
   <si>
     <t>Coverage.subscriberId</t>
@@ -1078,7 +1078,7 @@
   </si>
   <si>
     <t>Typically, an individual uses policies which are theirs (relationship='self') before policies owned by others.  
-一般的に、個人は、他人が所有するポリシよりも、自分のポリシ（relationship='self'）を使用する。</t>
+一般的に、個人は、他人が所有するポリシーよりも、自分のポリシー（relationship='self'）を使用する。</t>
   </si>
   <si>
     <t>To determine relationship between the patient and the subscriber to determine coordination of benefits.  
@@ -1331,7 +1331,7 @@
   </si>
   <si>
     <t>A suite of codes indicating the cost category and associated amount which have been detailed in the policy and may have been  included on the health card.  
-ポリシに詳細が記載されており、ヘルスカードに含まれている可能性のあるコストカテゴリと関連する金額を示す一連のコード。</t>
+ポリシーに詳細が記載されており、ヘルスカードに含まれている可能性のあるコストカテゴリと関連する金額を示す一連のコード。</t>
   </si>
   <si>
     <t>For example by knowing the patient visit co-pay, the provider can collect the amount prior to undertaking treatment.  
@@ -1667,7 +1667,7 @@
   </si>
   <si>
     <t>The policy(s) which constitute this insurance coverage.  
-この保険の適用範囲を構成するポリシ。</t>
+この保険の適用範囲を構成するポリシー。</t>
   </si>
   <si>
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolvable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.  
